--- a/school/Thesis Documentation/Digital/Truth Tables.xlsx
+++ b/school/Thesis Documentation/Digital/Truth Tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Files\GitHub\Computer_HTL\school\Thesis Documentation\Digital\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB6FA6F-BF83-43D2-97B9-DA02F651B16E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07837981-B13F-4737-8197-5CD940D5C54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40515" yWindow="-2535" windowWidth="11145" windowHeight="12555" xr2:uid="{1AF1B4DE-1790-45F4-9211-6E5630C531E9}"/>
   </bookViews>
@@ -43,9 +43,6 @@
     <t>B</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>AND</t>
   </si>
   <si>
@@ -71,6 +68,9 @@
   </si>
   <si>
     <t>xor</t>
+  </si>
+  <si>
+    <t>Q</t>
   </si>
 </sst>
 </file>
@@ -279,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -311,36 +311,35 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -683,262 +682,258 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="19"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="20"/>
+      <c r="B3" s="17">
+        <v>0</v>
+      </c>
+      <c r="C3" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="20"/>
+      <c r="B4" s="18">
+        <v>1</v>
+      </c>
+      <c r="C4" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="9"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="10"/>
-    </row>
-    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="19"/>
+      <c r="B8" s="3">
+        <v>0</v>
+      </c>
+      <c r="C8" s="4">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="19"/>
+      <c r="B9" s="5">
+        <v>0</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1</v>
+      </c>
+      <c r="D9" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="19"/>
+      <c r="B10" s="5">
+        <v>1</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0</v>
+      </c>
+      <c r="D10" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="19"/>
+      <c r="B11" s="7">
+        <v>1</v>
+      </c>
+      <c r="C11" s="8">
+        <v>1</v>
+      </c>
+      <c r="D11" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="F13" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="11"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9"/>
-      <c r="B3" s="20">
-        <v>0</v>
-      </c>
-      <c r="C3" s="16">
-        <v>1</v>
-      </c>
-      <c r="D3" s="11"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="9"/>
-      <c r="B4" s="21">
-        <v>1</v>
-      </c>
-      <c r="C4" s="18">
-        <v>0</v>
-      </c>
-      <c r="D4" s="11"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="11"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+    </row>
+    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
-      <c r="C8" s="4">
-        <v>0</v>
-      </c>
-      <c r="D8" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="5">
-        <v>0</v>
-      </c>
-      <c r="C9" s="6">
-        <v>1</v>
-      </c>
-      <c r="D9" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
-      <c r="B10" s="5">
-        <v>1</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0</v>
-      </c>
-      <c r="D10" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
-      <c r="B11" s="7">
-        <v>1</v>
-      </c>
-      <c r="C11" s="8">
-        <v>1</v>
-      </c>
-      <c r="D11" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="10" t="s">
+      <c r="B14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="19"/>
+      <c r="B15" s="3">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0</v>
+      </c>
+      <c r="D15" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="19"/>
+      <c r="B16" s="5">
+        <v>0</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="19"/>
+      <c r="B17" s="5">
+        <v>1</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="19"/>
+      <c r="B18" s="7">
+        <v>1</v>
+      </c>
+      <c r="C18" s="8">
+        <v>1</v>
+      </c>
+      <c r="D18" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="F13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
-      <c r="B15" s="3">
-        <v>0</v>
-      </c>
-      <c r="C15" s="4">
-        <v>0</v>
-      </c>
-      <c r="D15" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
-      <c r="B16" s="5">
-        <v>0</v>
-      </c>
-      <c r="C16" s="6">
-        <v>1</v>
-      </c>
-      <c r="D16" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="10"/>
-      <c r="B17" s="5">
-        <v>1</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0</v>
-      </c>
-      <c r="D17" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
-      <c r="B18" s="7">
-        <v>1</v>
-      </c>
-      <c r="C18" s="8">
-        <v>1</v>
-      </c>
-      <c r="D18" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B20" s="10" t="s">
+      <c r="B21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-    </row>
-    <row r="21" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
+      <c r="A22" s="19"/>
       <c r="B22" s="3">
         <v>0</v>
       </c>
       <c r="C22" s="4">
         <v>0</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="13">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
+      <c r="A23" s="19"/>
       <c r="B23" s="5">
         <v>0</v>
       </c>
       <c r="C23" s="6">
         <v>1</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
+      <c r="A24" s="19"/>
       <c r="B24" s="5">
         <v>1</v>
       </c>
       <c r="C24" s="6">
         <v>0</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
+      <c r="A25" s="19"/>
       <c r="B25" s="7">
         <v>1</v>
       </c>
       <c r="C25" s="8">
         <v>1</v>
       </c>
-      <c r="D25" s="18">
+      <c r="D25" s="15">
         <v>0</v>
       </c>
     </row>

--- a/school/Thesis Documentation/Digital/Truth Tables.xlsx
+++ b/school/Thesis Documentation/Digital/Truth Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Files\GitHub\Computer_HTL\school\Thesis Documentation\Digital\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07837981-B13F-4737-8197-5CD940D5C54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95EB9844-B32C-440F-AB4C-F331F40996DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40515" yWindow="-2535" windowWidth="11145" windowHeight="12555" xr2:uid="{1AF1B4DE-1790-45F4-9211-6E5630C531E9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{1AF1B4DE-1790-45F4-9211-6E5630C531E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
   <si>
     <t>A</t>
   </si>
@@ -71,6 +71,39 @@
   </si>
   <si>
     <t>Q</t>
+  </si>
+  <si>
+    <t>In1</t>
+  </si>
+  <si>
+    <t>In2</t>
+  </si>
+  <si>
+    <t>Out</t>
+  </si>
+  <si>
+    <t>full adder</t>
+  </si>
+  <si>
+    <t>driver</t>
+  </si>
+  <si>
+    <t>In</t>
+  </si>
+  <si>
+    <t>En</t>
+  </si>
+  <si>
+    <t>val</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Cout</t>
+  </si>
+  <si>
+    <t>Cin</t>
   </si>
 </sst>
 </file>
@@ -102,7 +135,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -270,6 +303,35 @@
       <left/>
       <right/>
       <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
         <color auto="1"/>
       </top>
       <bottom/>
@@ -279,7 +341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -340,6 +402,31 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -675,19 +762,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8198B413-3591-4CF2-8CE7-0C3C8ABF2654}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B1" s="19" t="s">
         <v>7</v>
       </c>
       <c r="C1" s="19"/>
     </row>
-    <row r="2" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>5</v>
       </c>
@@ -697,8 +784,20 @@
       <c r="C2" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H2" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="N2" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="24"/>
+      <c r="P2" s="23"/>
+    </row>
+    <row r="3" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20"/>
       <c r="B3" s="17">
         <v>0</v>
@@ -706,8 +805,32 @@
       <c r="C3" s="13">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H3" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" s="27" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="20"/>
       <c r="B4" s="18">
         <v>1</v>
@@ -715,20 +838,83 @@
       <c r="C4" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H4" s="21">
+        <v>0</v>
+      </c>
+      <c r="I4" s="21">
+        <v>0</v>
+      </c>
+      <c r="J4" s="21">
+        <v>0</v>
+      </c>
+      <c r="K4" s="29">
+        <v>0</v>
+      </c>
+      <c r="L4" s="21">
+        <v>0</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4" s="25">
+        <v>0</v>
+      </c>
+      <c r="P4" s="28" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="9"/>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H5" s="22">
+        <v>0</v>
+      </c>
+      <c r="I5" s="22">
+        <v>0</v>
+      </c>
+      <c r="J5" s="22">
+        <v>1</v>
+      </c>
+      <c r="K5" s="28">
+        <v>1</v>
+      </c>
+      <c r="L5" s="22">
+        <v>0</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="O5" s="25">
+        <v>1</v>
+      </c>
+      <c r="P5" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="20"/>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H6" s="22">
+        <v>0</v>
+      </c>
+      <c r="I6" s="22">
+        <v>1</v>
+      </c>
+      <c r="J6" s="22">
+        <v>0</v>
+      </c>
+      <c r="K6" s="28">
+        <v>1</v>
+      </c>
+      <c r="L6" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>2</v>
       </c>
@@ -741,8 +927,23 @@
       <c r="D7" s="12" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H7" s="22">
+        <v>0</v>
+      </c>
+      <c r="I7" s="22">
+        <v>1</v>
+      </c>
+      <c r="J7" s="22">
+        <v>1</v>
+      </c>
+      <c r="K7" s="28">
+        <v>0</v>
+      </c>
+      <c r="L7" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="19"/>
       <c r="B8" s="3">
         <v>0</v>
@@ -753,8 +954,23 @@
       <c r="D8" s="13">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H8" s="22">
+        <v>1</v>
+      </c>
+      <c r="I8" s="22">
+        <v>0</v>
+      </c>
+      <c r="J8" s="22">
+        <v>0</v>
+      </c>
+      <c r="K8" s="28">
+        <v>1</v>
+      </c>
+      <c r="L8" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="19"/>
       <c r="B9" s="5">
         <v>0</v>
@@ -765,8 +981,23 @@
       <c r="D9" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H9" s="22">
+        <v>1</v>
+      </c>
+      <c r="I9" s="22">
+        <v>0</v>
+      </c>
+      <c r="J9" s="22">
+        <v>1</v>
+      </c>
+      <c r="K9" s="28">
+        <v>0</v>
+      </c>
+      <c r="L9" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="19"/>
       <c r="B10" s="5">
         <v>1</v>
@@ -777,8 +1008,23 @@
       <c r="D10" s="14">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H10" s="22">
+        <v>1</v>
+      </c>
+      <c r="I10" s="22">
+        <v>1</v>
+      </c>
+      <c r="J10" s="22">
+        <v>0</v>
+      </c>
+      <c r="K10" s="28">
+        <v>0</v>
+      </c>
+      <c r="L10" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="19"/>
       <c r="B11" s="7">
         <v>1</v>
@@ -789,14 +1035,29 @@
       <c r="D11" s="15">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="H11" s="22">
+        <v>1</v>
+      </c>
+      <c r="I11" s="22">
+        <v>1</v>
+      </c>
+      <c r="J11" s="22">
+        <v>1</v>
+      </c>
+      <c r="K11" s="28">
+        <v>1</v>
+      </c>
+      <c r="L11" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B13" s="19" t="s">
         <v>9</v>
       </c>
@@ -806,7 +1067,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>3</v>
       </c>
@@ -820,7 +1081,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="19"/>
       <c r="B15" s="3">
         <v>0</v>
@@ -832,7 +1093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="19"/>
       <c r="B16" s="5">
         <v>0</v>
@@ -938,7 +1199,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="N2:P2"/>
     <mergeCell ref="A7:A11"/>
     <mergeCell ref="A14:A18"/>
     <mergeCell ref="A21:A25"/>
@@ -949,5 +1212,6 @@
     <mergeCell ref="B20:D20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>